--- a/tables/String.xlsx
+++ b/tables/String.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.25" customWidth="1" min="1" max="1"/>
@@ -542,11 +542,6 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
           <t>Note</t>
         </is>
       </c>
@@ -567,11 +562,6 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
           <t>주인공</t>
         </is>
       </c>
@@ -590,11 +580,6 @@
           <t>허수귀</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -610,11 +595,6 @@
           <t>지게귀</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -632,11 +612,6 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
           <t>변종</t>
         </is>
       </c>
@@ -657,11 +632,6 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
           <t>변종</t>
         </is>
       </c>
@@ -682,11 +652,6 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
           <t>보스</t>
         </is>
       </c>
@@ -705,11 +670,6 @@
           <t>발골칼</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -727,11 +687,6 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
           <t>완성판</t>
         </is>
       </c>
@@ -752,11 +707,6 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
           <t>완성판</t>
         </is>
       </c>
@@ -775,11 +725,6 @@
           <t>결박 가르기</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -795,11 +740,6 @@
           <t>도화골</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -817,11 +757,6 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
           <t>이름 미정</t>
         </is>
       </c>
@@ -842,11 +777,6 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
           <t>이름 미정</t>
         </is>
       </c>
@@ -867,11 +797,6 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
           <t>이름 미정</t>
         </is>
       </c>
@@ -890,11 +815,6 @@
           <t>베기</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -910,11 +830,6 @@
           <t>베기</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -930,11 +845,6 @@
           <t>내리베기</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -950,11 +860,6 @@
           <t>공중 베기</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -970,11 +875,6 @@
           <t>해체</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -990,11 +890,6 @@
           <t>결박 가르기</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1012,11 +907,6 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
           <t>회피 확률 발동 시 표시</t>
         </is>
       </c>
@@ -1035,11 +925,6 @@
           <t>약초</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -1057,11 +942,6 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
           <t>장부방</t>
         </is>
       </c>
@@ -1082,11 +962,6 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
           <t>저장 지점</t>
         </is>
       </c>
@@ -1105,11 +980,6 @@
           <t>TO BE CONTINUED</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -1126,11 +996,6 @@
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>로딩씬</t>
         </is>

--- a/tables/String.xlsx
+++ b/tables/String.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>표시 텍스트.</t>
+          <t>CSV,표시 텍스트.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>

--- a/tables/String.xlsx
+++ b/tables/String.xlsx
@@ -670,6 +670,11 @@
           <t>발골칼</t>
         </is>
       </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>아이템 아님(해체 연출용). 지금 참조하는 행 없음</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -687,7 +692,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>완성판</t>
+          <t>시작 무기</t>
         </is>
       </c>
     </row>
@@ -807,7 +812,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>발골칼 1타</t>
+          <t>버선칼 1타</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -822,7 +827,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>발골칼 2타</t>
+          <t>버선칼 2타</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -837,7 +842,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>발골칼 3타</t>
+          <t>버선칼 3타</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
